--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-001_ログイン_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-001_ログイン_オンライン詳細設計書.xlsx
@@ -273,7 +273,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="3171825"/>
+    <ext cx="10953750" cy="3429000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="8486775"/>
+    <ext cx="10953750" cy="9144000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -330,10 +330,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10020300"/>
+    <ext cx="8572500" cy="12392025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-001 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-001 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E20"/>
+  <dimension ref="A2:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -853,12 +853,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>ユーザー不存在／status≠ACTIVE／パスワード不一致（ログイン時）。トークンなし・不正・期限切れ（全認証必須 API。文言は『認証情報が無効、または有効期限が切れています。再度ログインしてください。』、発生箇所は RestAuthenticationEntryPoint）</t>
+          <t>ユーザー不存在／status≠ACTIVE／パスワード不一致（ログイン時。5 回目の失敗も E-001）。トークンなし・不正・期限切れ（全認証必須 API。文言は『認証が必要です。再度ログインしてください。』、発生箇所は SecurityConfig の authenticationEntryPoint）</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>AuthService#login／RestAuthenticationEntryPoint#commence</t>
+          <t>AuthService#login／SecurityConfig#authenticationEntryPoint</t>
         </is>
       </c>
     </row>
@@ -880,225 +880,249 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>権限不足（@PreAuthorize／フィルタ段階の認可）。本処理（ログイン）自体では発生しないが、共通基盤として定義</t>
+          <t>権限不足（フィルタ段階の認可／@PreAuthorize）。本処理（ログイン）自体では発生しないが、共通基盤として定義</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler#handleAccessDenied／RestAccessDeniedHandler#handle</t>
+          <t>SecurityConfig#accessDeniedHandler／GlobalExceptionHandler#handleAccessDenied</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>E-017</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>アカウントがロックされています。しばらくしてから再度お試しください。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ロック中（users.locked_until が現在日時より後）。パスワード照合より前に判定するため、正しいパスワードでも発生する</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>AuthService#login</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="49" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>E-002</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>項目別メッセージ（4. 参照）／入力内容が正しくありません。</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>入力チェック不正／JSON不正／パス・クエリパラメータの型不一致（GlobalExceptionHandler#handleTypeMismatch）</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>@Valid／GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>E-012</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>上記以外の予期しない例外（DB 接続断など）</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler#handleOther</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>8.2 ログ出力</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>出力内容</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>出力禁止</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>出力箇所</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>予期しない例外（E-012）</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Unexpected error ＋スタックトレース</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>パスワード・ハッシュ・トークン・リクエスト本文</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>開発用ユーザー投入時</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Dev seed users created (4 users).</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>初期パスワード</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DevDataInitializer</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>開発用ユーザー投入時</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Dev seed users created ({} users).</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワード</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DevDataInitializer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>初期管理者作成時</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Bootstrap admin created: {メールアドレス}</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワード</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>ログイン成功・失敗</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>ログイン成功・失敗・ロック</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>現時点では出力しない（監査ログは今後検討）</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>8.3 セキュリティ・権限上の考慮</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>原因の非開示</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>E-001 は原因（不存在／無効／不一致）を区別せず同一応答にする。</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー不存在時は BCrypt 照合を行わないため、応答時間にわずかな差が出る（タイミング攻撃の余地）。学習用途のため現時点では許容。</t>
-        </is>
-      </c>
+      <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10" t="n"/>
@@ -1106,58 +1130,168 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>未対応（今後）</t>
+          <t>ログインロック</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>連続失敗によるロック／ログイン履歴／トークン失効（ログアウト時の無効化）。※ 期限切れ・不正トークン時の JSON 形式の 401 応答は RestAuthenticationEntryPoint で対応済み。</t>
+          <t>連続 5 回のパスワード誤りで 30 分ロック（総当たり攻撃の対策）。ロック中は正しいパスワードでも E-017。失敗回数は users.failed_login_count に保存し、@Transactional(noRollbackFor=BusinessException.class) で確実にコミットする。ユーザー不存在・INACTIVE は回数を数えない。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19" ht="34" customHeight="1">
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>メールアドレスの正規化</t>
+          <t>原因の非開示</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>保存時・検索時とも trim().toLowerCase(Locale.ROOT) で正規化する。大文字小文字違いによる重複登録（uq_users_1 の回避）と、ログイン時の入力ゆれを防ぐ。ログの出力では email 自体を出さない。</t>
+          <t>E-001 は原因（不存在／無効／不一致）を区別せず同一応答にする。</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="n"/>
     </row>
-    <row r="20" ht="34" customHeight="1">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>認証・認可エラーの形式</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>401 / 403 を空ボディではなく ErrorResponse(JSON) で返す。原因（署名不正・期限切れ等）は応答に含めない。</t>
+          <t>ユーザー不存在時は BCrypt 照合を行わないため、応答時間にわずかな差が出る（タイミング攻撃の余地）。学習用途のため現時点では許容。</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="10" t="n"/>
     </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>未対応（今後）</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>ログイン履歴（監査ログ）／トークン失効（ログアウト時の無効化）／管理者によるロック解除操作（現状は 30 分経過で自動解除。locked_until を DB で NULL にすれば手動解除可）。</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="49" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>メールアドレスの正規化</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>保存時・検索時とも trim().toLowerCase(Locale.ROOT) で正規化する。大文字小文字違いによる重複登録（uq_users_1 の回避）と、ログイン時の入力ゆれを防ぐ。ログ出力では通常 email を出さない（例外：初期管理者作成時のログ『Bootstrap admin created: {email}』のみメールアドレスを出す。実装どおり）。現行コードは正規化を AuthService#login 内で直接行っており、共通化（EmailNormalizer）は ONL-014 実装時。</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>認証・認可エラーの形式</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>401 / 403 を空ボディではなく ErrorResponse(JSON) で返す（SecurityConfig の authenticationEntryPoint / accessDeniedHandler）。原因（署名不正・期限切れ等）は応答に含めない。</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>トークン有効期間</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>JWT は 2 時間（kintaiflow.jwt.expiration-hours=2）。無効化・ロール変更は有効期限まで旧権限のまま（ロールの最終判断は DB の users.role / status で行う処理あり）。</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>初期パスワードの強制変更</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>must_change_password=true のユーザーはログイン応答の mustChangePassword で画面に変更を促す。画面（Vue Router のガード）は変更完了まで /password へ固定する。【既知課題】サーバー側の強制は未実装：mustChangePassword=true のユーザーも、取得済みトークンで POST /api/auth/password 以外の API を呼べてしまう（画面を経由しない直接呼び出し）。対策案：JWT の claim に mustChange を載せ、フィルタで /api/auth/password 以外を 403 にする（後続改修）。変更は ONL-023。</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>初期管理者</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer は users が空の初回起動時のみ動作。ポリシー違反のパスワードは起動失敗（fail-fast）。BOOTSTRAP_ADMIN_EMAIL / BOOTSTRAP_ADMIN_PASSWORD は .env（Git 管理外）に置く。</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="49" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>管理者によるロック解除（未実装）</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §4 は『管理者が解除可』とするが、現行は 30 分経過による自動解除のみ（locked_until を DB で NULL にすれば手動解除可）。管理画面からの解除操作は ONL-014 側の追加課題。</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B17:E17"/>
+  <mergeCells count="13">
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1170,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E32"/>
+  <dimension ref="A2:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1236,7 +1370,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>LoginResponse（token, userId, name, role）が返る</t>
+          <t>LoginResponse（token, userId, name, role, mustChangePassword）が返る</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1409,7 +1543,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>200、body に token / userId / name / role</t>
+          <t>200、body に token / userId / name / role / mustChangePassword</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1541,7 +1675,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>12</t>
@@ -1559,7 +1693,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>401 E-001（JSON の ErrorResponse）</t>
+          <t>401 E-001（JSON の ErrorResponse、message『認証が必要です。再度ログインしてください。』）</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1651,7 +1785,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>exp − iat = 8時間</t>
+          <t>exp − iat = 2時間</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
@@ -1717,11 +1851,11 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>EmailNormalizer 適用の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
+          <t>AuthService 内の正規化（trim＋小文字）の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>16</t>
@@ -1734,17 +1868,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>EmailNormalizer#normalize(null) / ("") / (" A@B.c ")</t>
+          <t>email="   "（空白のみ）</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>null / "" / "a@b.c"</t>
+          <t>400 E-002「メールアドレスは必須入力です。」。Service は呼ばれない</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Locale.ROOT（トルコ語ロケールで "I" → "i"）</t>
+          <t>@NotBlank。EmailNormalizer（未実装）のテストは ONL-014 実装時に追加</t>
         </is>
       </c>
     </row>
@@ -1766,16 +1900,16 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>401、{code:"E-001", message:"認証情報が無効、または有効期限が切れています。…", fieldErrors:[]}（Content-Type: application/json）</t>
+          <t>401、{code:"E-001", message:"認証が必要です。再度ログインしてください。", fieldErrors:[]}（Content-Type: application/json）</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
+          <t>SecurityConfig#authenticationEntryPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>18</t>
@@ -1798,11 +1932,11 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>oauth2ResourceServer 側の entryPoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1">
+          <t>oauth2ResourceServer 側の entryPoint（同じ writeError）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>19</t>
@@ -1825,7 +1959,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>handleAccessDenied（@PreAuthorize）</t>
+          <t>@PreAuthorize 使用 API の実装後に確認（handleAccessDenied）</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1990,429 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>9.5 ログインロック・強制変更（C1 追加観点）</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>ログイン成功時に failed_login_count=3</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>failed_login_count が 0 に更新され save が 1 回。LoginResponse を返す</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>失敗回数 0・locked_until なしで成功</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>save は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>不要な UPDATE をしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword=true のユーザーで成功</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>LoginResponse.mustChangePassword = true</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワード</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>パスワード不一致（failed_login_count=0）</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>E-001 / 401。failed_login_count=1 で save</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>4 回失敗済み（failed_login_count=4）で 5 回目の不一致</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>E-001 / 401。locked_until = now+30分、failed_login_count=0 で save</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>5 回目で E-001 のままロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>locked_until が未来（正しいパスワード）</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>E-017 / 423。matches は呼ばれない・save も呼ばれない</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ロック中は照合しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>locked_until が過去（正しいパスワード）</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ログイン成功。locked_until が NULL に更新される</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>自動解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>status=INACTIVE でパスワード不一致</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>E-001 / 401。failed_login_count は変化しない</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>MockMvc 結合：ロック中に API を呼ぶ</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 423、{code:"E-017", message:"アカウントがロックされています。…"}</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>423 の応答</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>@Transactional(noRollbackFor) の確認（結合）</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>E-001 を返した後でも DB の failed_login_count が加算されている</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>ロールバックされない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="49" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer：users 空・設定あり</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN 1 名（must_change_password=true・email 小文字・department_id=1）が作成される</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer：users 非空 / 設定なし</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>何も作成されない</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>DevData 先行時も何もしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer：パスワード 8 文字</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>IllegalStateException（起動失敗）</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>fail-fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>GET /actuator/health（認証なし）</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>permitAll</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1874,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1956,6 +2507,30 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="199" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>・設計同期（実装反映）：ログイン強化（メール trim＋小文字・ロック判定 E-017/423・連続 5 回失敗で 30 分ロック・成功時リセット・@Transactional(noRollbackFor=BusinessException)・LoginResponse に mustChangePassword）、JWT 有効 2 時間、401/403 の JSON を SecurityConfig のラムダ実装（writeError）に合わせて訂正、/actuator/health 公開・CORS 設定化、Flyway 移行（ddl-auto=validate）、BootstrapAdminInitializer 追加・DevDataInitializer を 100 名に改訂
+・実コードとの照合で修正：画面遷移先を SCR-007 に訂正／EmailNormalizer を『未実装（現行は AuthService 内で直接正規化）』と明記／初期化クラスの @Transactional 記述・validatePolicy 引数・ログ出力・環境変数名（BOOTSTRAP_ADMIN_*）を実装に合わせて訂正／部署ごとの上長・社員の ID 範囲を訂正／mustChangePassword のサーバー側強制が未実装であることを既知課題として明記</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1969,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F40"/>
+  <dimension ref="A2:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2056,7 +2631,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -2064,7 +2639,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードで利用者を認証し、以降の API 呼び出しに使う認証トークン（JWT）を発行する。あわせて、後続の全 API が前提とする共通の認証・認可エラー応答（トークン不正・期限切れは 401 / E-001、権限不足は 403 / E-010、いずれも JSON の ErrorResponse）を SecurityConfig / GlobalExceptionHandler に集約して定義する（6.x「共通基盤への追加改修」）。</t>
+          <t>メールアドレスとパスワードで利用者を認証し、以降の API 呼び出しに使う認証トークン（JWT。有効 2 時間）を発行する。連続 5 回のパスワード誤りでアカウントを 30 分ロックし（users.failed_login_count / locked_until）、初期パスワードのままのユーザーには mustChangePassword=true を返してパスワード変更（ONL-023）へ誘導する。あわせて、後続の全 API が前提とする共通の認証・認可エラー応答（トークン不正・期限切れ・認証なしは 401 / E-001、権限不足は 403 / E-010、いずれも JSON の ErrorResponse）を SecurityConfig / GlobalExceptionHandler に集約して定義する（6.x「共通基盤への追加改修」）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2104,7 +2679,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2112,7 +2687,8 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>データ更新なし（users は参照のみ）。レスポンスに JWT を含む。</t>
+          <t>成功時: failed_login_count ≠ 0 または locked_until ≠ NULL なら 0 / NULL に戻して更新（それ以外は更新なし）。レスポンスに JWT と mustChangePassword を含む。
+パスワード不一致時: failed_login_count を +1 して更新（5 回目は locked_until = 現在日時（JST）+ 30 分、failed_login_count = 0）。E-001 を返しても更新は確定（コミット）する。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2128,7 +2704,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>users: R</t>
+          <t>users: R/U</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2136,7 +2712,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>トランザクション</t>
@@ -2144,7 +2720,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>読み取り専用（AuthService#login に @Transactional(readOnly = true)）</t>
+          <t>AuthService#login に @Transactional(noRollbackFor = BusinessException.class)（読み書き）。パスワード不一致で BusinessException(E-001) を投げても、失敗回数・ロック日時の UPDATE をロールバックせずコミットするために必須（readOnly や既定のままだと失敗回数が保存されない）。</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2217,7 +2793,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>E-001 / E-002 / E-012</t>
+          <t>E-001 / E-002 / E-010 / E-012 / E-017（ログインロック）</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -2277,7 +2853,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>users テーブル</t>
+          <t>users テーブル（failed_login_count / locked_until / must_change_password / password_changed_at）</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -2324,234 +2900,210 @@
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="10" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>KF-BD-010</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>非機能設計書</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>パスワードポリシー・ログインロック・トークン有効期間（2 時間）</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更（オンライン詳細設計書）</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword=true のユーザーが POST /api/auth/password で変更する。AuthService#validatePolicy を共用</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>controller</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>AuthController</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>リクエスト受付・Service 呼出・応答返却</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>controller/AuthController.java</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>AuthService</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ログイン業務ロジック（ONL-001 本体）</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>service/AuthService.java</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>controller</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>AuthController</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>リクエスト受付・Service 呼出・応答返却</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>controller/AuthController.java</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="79" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>AuthService</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>ログイン業務ロジック（ONL-001 本体）。ロック判定・失敗回数管理を含む。changePassword / validatePolicy は ONL-023 で追加</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>service/AuthService.java</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>UserRepository</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>users のメール検索</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>users のメール検索 findByEmail</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>repository/UserRepository.java</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>users テーブルのマッピング</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>users テーブルのマッピング（failedLoginCount / lockedUntil / mustChangePassword / passwordChangedAt を含む）</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>entity/User.java</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>LoginRequest</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>リクエスト＋入力チェック定義</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>dto/LoginRequest.java</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>LoginResponse</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>正常応答</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>dto/LoginResponse.java</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2568,127 +3120,127 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>LoginRequest</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>リクエスト＋入力チェック定義</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>dto/LoginRequest.java</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>LoginResponse</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>正常応答（token / userId / name / role / mustChangePassword）</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>dto/LoginResponse.java</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
           <t>ErrorResponse</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>共通エラー応答</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>dto/ErrorResponse.java</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>security</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>JwtService</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>JWT 発行</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>JWT 発行（有効 2 時間）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>security/JwtService.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="49" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>RestAuthenticationEntryPoint</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>AuthenticationEntryPoint</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>未認証・トークン不正・期限切れを 401 / E-001 の JSON で返す</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>security/RestAuthenticationEntryPoint.java</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>新規（共通基盤への追加改修）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>RestAccessDeniedHandler</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>AccessDeniedHandler</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>security/RestAccessDeniedHandler.java</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>新規（共通基盤への追加改修）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="64" customHeight="1">
+    <row r="36" ht="124" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>util</t>
@@ -2706,7 +3258,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>メールアドレスの正規化 normalize（trim＋小文字化）。保存時・検索時に共通利用（ONL-014 も使用）</t>
+          <t>【未実装・設計案】メールアドレスの正規化 normalize（trim＋小文字化）。現行コードは AuthService#login 内で trim().toLowerCase(Locale.ROOT) を直接実行しており、ONL-014（ユーザー管理）の実装時に共通化する予定</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2716,7 +3268,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>新規（未実装。現行は AuthService 内で直接実施）</t>
         </is>
       </c>
     </row>
@@ -2784,7 +3336,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1">
+    <row r="39" ht="64" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>config</t>
@@ -2802,7 +3354,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義</t>
+          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義。401 / 403 の JSON 応答（writeError）を含む</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -2816,7 +3368,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="49" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>config</t>
@@ -2834,7 +3386,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>開発用テストユーザー投入（本番では無効）</t>
+          <t>開発用テストユーザー 100 名の投入（@Order(1)。seed-password 設定時のみ）</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -2844,16 +3396,50 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>新規（ONL-001 で 4 名→100 名に改訂）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>CommandLineRunner</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>初期管理者（ADMIN）1 名の作成（@Order(2)。users が空かつ bootstrap 設定が揃っているときのみ）</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>config/BootstrapAdminInitializer.java</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>新規（C6）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
@@ -2862,12 +3448,12 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
@@ -2961,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F21"/>
+  <dimension ref="A2:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3154,7 +3740,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>JWT（HS256、8時間有効）</t>
+          <t>JWT（HS256、2時間有効）</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -3232,82 +3818,83 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
-    <row r="14" ht="94" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="14" ht="49" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>要パスワード変更</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>users.must_change_password。true のとき画面はパスワード変更（SCR-007。ルート /password）へ遷移させる（初期パスワード・管理者再設定後）。ログイン画面は res.mustChangePassword を見て router.push('/password') する</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="109" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>レスポンス例</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>{
   "token": "eyJhbGciOiJIUzI1NiJ9.xxxxx.xxxxx",
   "userId": 3,
   "name": "山田 太郎",
-  "role": "EMPLOYEE"
+  "role": "EMPLOYEE",
+  "mustChangePassword": false
 }</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>4.3 レスポンス（エラー）  共通形式 ErrorResponse</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>項目名</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>論理名</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="10" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>エラーコード</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>E-xxx（8. エラー一覧）</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -3316,12 +3903,12 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>code</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>メッセージ</t>
+          <t>エラーコード</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -3331,7 +3918,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>画面に表示する文言（日本語）</t>
+          <t>E-xxx（8. エラー一覧）</t>
         </is>
       </c>
       <c r="E19" s="9" t="n"/>
@@ -3340,62 +3927,91 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>fieldErrors</t>
+          <t>message</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>項目別エラー</t>
+          <t>メッセージ</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
+          <t>画面に表示する文言（日本語）</t>
         </is>
       </c>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="94" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>fieldErrors</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>項目別エラー</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="199" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>HTTP 401
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>HTTP 401（メール不一致・無効ユーザー・パスワード不一致はすべて同一）
 { "code": "E-001", "message": "メールアドレスまたはパスワードが正しくありません。", "fieldErrors": [] }
+HTTP 423（ロック中。ロック期限前は正しいパスワードでも同じ）
+{ "code": "E-017", "message": "アカウントがロックされています。しばらくしてから再度お試しください。", "fieldErrors": [] }
 HTTP 400
 { "code": "E-002", "message": "メールアドレスは必須入力です。",
-  "fieldErrors": [ { "field": "email", "message": "メールアドレスは必須入力です。" } ] }</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
+  "fieldErrors": [ { "field": "email", "message": "メールアドレスは必須入力です。" } ] }
+HTTP 401（他 API でトークンなし・期限切れ・不正。SecurityConfig の authenticationEntryPoint が返す JSON）
+{ "code": "E-001", "message": "認証が必要です。再度ログインしてください。", "fieldErrors": [] }</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B21:F21"/>
+  <mergeCells count="16">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="D21:F21"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
@@ -3410,7 +4026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F12"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3494,7 +4110,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>入力の email を EmailNormalizer#normalize（trim().toLowerCase(Locale.ROOT)）で正規化し、SELECT * FROM users WHERE email = ?（UserRepository#findByEmail）</t>
+          <t>入力の email を trim().toLowerCase(Locale.ROOT)（AuthService#login 内で直接実行）で正規化し、SELECT * FROM users WHERE email = ?（UserRepository#findByEmail）</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3508,7 +4124,7 @@
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>③</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3518,7 +4134,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Optional が空なら失敗</t>
+          <t>Optional が空なら失敗。BCrypt 照合は行わない</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3532,7 +4148,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3542,7 +4158,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>INACTIVE は失敗</t>
+          <t>INACTIVE は失敗（失敗回数は加算しない）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3553,68 +4169,68 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="49" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BCrypt でパスワード一致？</t>
+          <t>ロック中ではないか？</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>PasswordEncoder#matches(入力値, password_hash)</t>
+          <t>users.locked_until が NULL でなく、現在日時（JST）より後ならロック中。正しいパスワードでも拒否する（パスワード照合より前に判定）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>判定（No → E-001 を返却  HTTP 401）</t>
+          <t>判定（No → E-017 を返却  HTTP 423）</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="94" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑥</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>JWT を生成（HS256 / 有効8時間）</t>
+          <t>BCrypt でパスワード一致？</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>JwtService#issue(user)</t>
+          <t>PasswordEncoder#matches(入力値, password_hash)。不一致のときは failed_login_count + 1 を保存する（5 回目は locked_until = 現在日時 + 30 分、failed_login_count = 0 にして保存）。保存は例外送出前に行い、noRollbackFor によりコミットされる</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>処理</t>
+          <t>判定（No → E-001 を返却  HTTP 401）</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>⑥</t>
+          <t>⑦</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>レスポンス返却 {token, userId, name, role}</t>
+          <t>失敗回数をリセット</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>LoginResponse を生成して返す</t>
+          <t>failed_login_count ≠ 0 または locked_until ≠ NULL の場合のみ、failed_login_count = 0・locked_until = NULL に更新（通常ログインでは UPDATE しない）</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3625,26 +4241,76 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>5.2 処理フロー図</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>JWT を生成（HS256 / 有効2時間）</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>JwtService#issue(user)。有効時間は kintaiflow.jwt.expiration-hours（2）</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>レスポンス返却 {token, userId, name, role, mustChangePassword}</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>LoginResponse を生成して返す。mustChangePassword は users.must_change_password</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>5.2 処理フロー図</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
@@ -3662,7 +4328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F140"/>
+  <dimension ref="A2:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3926,7 +4592,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ユーザー検索・有効確認・パスワード照合を行い、成功時に LoginResponse を返す。</t>
+          <t>ユーザー検索・有効確認・ロック判定・パスワード照合・失敗回数管理を行い、成功時に LoginResponse を返す。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -3942,7 +4608,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+          <t>@Transactional(noRollbackFor = BusinessException.class)  ※クラスに @Service</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -3998,7 +4664,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>LoginResponse(token, userId, name, role)</t>
+          <t>LoginResponse(token, userId, name, role, mustChangePassword)</t>
         </is>
       </c>
       <c r="C22" s="9" t="n"/>
@@ -4006,7 +4672,7 @@
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="10" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>例外</t>
@@ -4014,7 +4680,8 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>BusinessException("E-001", 401)  ※原因を区別しない</t>
+          <t>BusinessException("E-001", 401)  ※原因を区別しない
+BusinessException("E-017", 423)  ※ロック中</t>
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
@@ -4022,7 +4689,7 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24" ht="154" customHeight="1">
+    <row r="24" ht="409" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4030,16 +4697,33 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>user = userRepository.findByEmail(EmailNormalizer.normalize(request.email()))     // ② trim＋小文字化して検索
-          .orElseThrow(AuthService::invalidCredentials);       // ② 存在しない → E-001
-if (!"ACTIVE".equals(user.getStatus()))                      // ③ 無効ユーザー → E-001
+          <t>String email = request.email().trim().toLowerCase(Locale.ROOT);     // ② 正規化
+User user = userRepository.findByEmail(email)
+        .orElseThrow(AuthService::invalidCredentials);                   // ③ 存在しない → E-001
+if (!"ACTIVE".equals(user.getStatus()))                                  // ④ 無効ユーザー → E-001
     throw invalidCredentials();
-if (!passwordEncoder.matches(request.password(),
-                             user.getPasswordHash()))          // ④ 不一致 → E-001
-    throw invalidCredentials();
-token = jwtService.issue(user);                                // ⑤ トークン発行
-return new LoginResponse(token, user.getId(),
-                         user.getName(), user.getRole());      // ⑥ 返却</t>
+LocalDateTime now = LocalDateTime.now(JST);
+if (user.getLockedUntil() != null &amp;&amp; user.getLockedUntil().isAfter(now))  // ⑤ ロック中 → E-017（423）
+    throw new BusinessException("E-017", "アカウントがロックされています。しばらくしてから再度お試しください。", HttpStatus.LOCKED);
+if (!passwordEncoder.matches(request.password(), user.getPasswordHash())) { // ⑥ 不一致
+    int count = user.getFailedLoginCount() + 1;
+    if (count &gt;= MAX_FAILED_ATTEMPTS) {                                   // 5 回目：30 分ロックしてカウントを 0 に戻す
+        user.setLockedUntil(now.plusMinutes(LOCK_MINUTES));
+        user.setFailedLoginCount(0);
+    } else {
+        user.setFailedLoginCount(count);
+    }
+    userRepository.save(user);                                           // 例外の前に保存（noRollbackFor でコミットされる）
+    throw invalidCredentials();                                          // 失敗は常に E-001
+}
+if (user.getFailedLoginCount() != 0 || user.getLockedUntil() != null) {   // ⑦ 成功：リセット
+    user.setFailedLoginCount(0);
+    user.setLockedUntil(null);
+    userRepository.save(user);
+}
+String token = jwtService.issue(user);                                   // ⑧
+return new LoginResponse(token, user.getId(), user.getName(),
+        user.getRole(), user.isMustChangePassword());                    // ⑨</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -4055,7 +4739,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>EmailNormalizer#normalize / UserRepository#findByEmail / PasswordEncoder#matches / JwtService#issue</t>
+          <t>UserRepository#findByEmail / PasswordEncoder#matches / UserRepository#save / JwtService#issue</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -4063,7 +4747,7 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="34" customHeight="1">
+    <row r="26" ht="94" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4071,8 +4755,11 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>③④は「||」で連結して1つの if にしてよい（status 不正の場合は BCrypt 照合を行わない＝短絡評価）。
-パスワード・ハッシュ・トークンをログに出力しない。</t>
+          <t>定数: MAX_FAILED_ATTEMPTS = 5、LOCK_MINUTES = 30、JST = ZoneId.of("Asia/Tokyo")。
+@Transactional(noRollbackFor = BusinessException.class) が必須：既定ではランタイム例外でロールバックされ、失敗回数の UPDATE が失われてロックが機能しない。
+ロック判定（⑤）をパスワード照合（⑥）より前に行うため、ロック中は正しいパスワードでも E-017。ロック中の試行では失敗回数を加算しない。
+ロック期限が過ぎたユーザーは failed_login_count = 0 から再開（5 回目で 0 に戻しているため）。locked_until は成功時に NULL へ戻す。
+ユーザー不存在・INACTIVE は E-001（失敗回数の対象外）。パスワード・ハッシュ・トークンをログに出力しない。</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -4132,7 +4819,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>E-001 の BusinessException を生成する。3つの失敗原因で同一の例外・文言を使うために共通化している。</t>
+          <t>E-001 の BusinessException を生成する。失敗原因（不存在・無効・不一致）で同一の例外・文言を使うために共通化している。</t>
         </is>
       </c>
       <c r="C31" s="9" t="n"/>
@@ -4257,7 +4944,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>6.4  RestAuthenticationEntryPoint#commence</t>
+          <t>6.4  SecurityConfig#writeError</t>
         </is>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -4274,7 +4961,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Security（AuthenticationEntryPoint。共通基盤への追加改修）</t>
+          <t>Security（401 / 403 の JSON 応答。securityFilterChain の authenticationEntryPoint / accessDeniedHandler から呼ぶ）</t>
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
@@ -4282,7 +4969,7 @@
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="10" t="n"/>
     </row>
-    <row r="42" ht="34" customHeight="1">
+    <row r="42" ht="19" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -4290,8 +4977,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>@Override
-public void commence(HttpServletRequest request, HttpServletResponse response, AuthenticationException ex) throws IOException</t>
+          <t>private static void writeError(HttpServletResponse res, int status, String code, String message) throws IOException</t>
         </is>
       </c>
       <c r="C42" s="9" t="n"/>
@@ -4307,7 +4993,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>認証が必要な API に、トークンなし・不正・期限切れでアクセスされたときの応答を、Spring 既定の空ボディではなく共通の ErrorResponse（JSON）で返す。</t>
+          <t>認証が必要な API に、トークンなし・不正・期限切れでアクセスされたとき（401 / E-001）、および権限不足のとき（403 / E-010）の応答を、Spring 既定の空ボディではなく共通の ErrorResponse 形式の JSON で返す。</t>
         </is>
       </c>
       <c r="C43" s="9" t="n"/>
@@ -4323,7 +5009,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>クラス: @Component（SecurityConfig から注入）</t>
+          <t>なし（oauth2ResourceServer のラムダから呼び出す private static メソッド）</t>
         </is>
       </c>
       <c r="C44" s="9" t="n"/>
@@ -4354,17 +5040,17 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>request</t>
+          <t>res</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>HttpServletRequest</t>
+          <t>HttpServletResponse</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>リクエスト</t>
+          <t>レスポンス（ここに JSON を書く）</t>
         </is>
       </c>
       <c r="D46" s="9" t="n"/>
@@ -4374,17 +5060,17 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>response</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>HttpServletResponse</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>レスポンス（ここに JSON を書く）</t>
+          <t>HTTP ステータス（401 / 403）</t>
         </is>
       </c>
       <c r="D47" s="9" t="n"/>
@@ -4394,17 +5080,17 @@
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>ex</t>
+          <t>code</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>AuthenticationException</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>認証失敗の原因（応答には出さない）</t>
+          <t>E-001 / E-010</t>
         </is>
       </c>
       <c r="D48" s="9" t="n"/>
@@ -4412,17 +5098,21 @@
       <c r="F48" s="10" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>なし（response に直接書き込む）</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="10" t="n"/>
@@ -4430,12 +5120,12 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>IOException（書き込み失敗。Servlet コンテナが処理）</t>
+          <t>なし（response に直接書き込む）</t>
         </is>
       </c>
       <c r="C50" s="9" t="n"/>
@@ -4443,20 +5133,15 @@
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="10" t="n"/>
     </row>
-    <row r="51" ht="94" customHeight="1">
+    <row r="51" ht="19" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>response.setStatus(HttpServletResponse.SC_UNAUTHORIZED);                        // 401
-response.setHeader("WWW-Authenticate", "Bearer");
-response.setContentType("application/json;charset=UTF-8");
-ErrorResponse body = new ErrorResponse("E-001",
-    "認証情報が無効、または有効期限が切れています。再度ログインしてください。", List.of());
-objectMapper.writeValue(response.getWriter(), body);                   // { code, message, fieldErrors:[] }</t>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>IOException（書き込み失敗。Servlet コンテナが処理）</t>
         </is>
       </c>
       <c r="C51" s="9" t="n"/>
@@ -4464,15 +5149,23 @@
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="10" t="n"/>
     </row>
-    <row r="52" ht="19" customHeight="1">
+    <row r="52" ht="154" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>ObjectMapper#writeValue（JSON 変換 Bean をコンストラクタ注入）</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>// securityFilterChain 内（oauth2ResourceServer のラムダ）
+.authenticationEntryPoint((req, res, ex) -&gt;
+    writeError(res, 401, "E-001", "認証が必要です。再度ログインしてください。"))
+.accessDeniedHandler((req, res, ex) -&gt;
+    writeError(res, 403, "E-010", "この操作を行う権限がありません。"))
+// writeError
+res.setStatus(status);
+res.setContentType("application/json;charset=UTF-8");
+res.getWriter().write("{\"code\":\"" + code + "\",\"message\":\"" + message + "\",\"fieldErrors\":[]}");</t>
         </is>
       </c>
       <c r="C52" s="9" t="n"/>
@@ -4480,17 +5173,15 @@
       <c r="E52" s="9" t="n"/>
       <c r="F52" s="10" t="n"/>
     </row>
-    <row r="53" ht="79" customHeight="1">
+    <row r="53" ht="19" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>コードは E-001（認証失敗）を使う。KF-BD-006 の E-001 は『メールアドレスまたはパスワードが正しくありません。』だが、トークン不正の文言としては不適切なため、E-001 の項目別文言として上記を使う（ONL-017 D-5 と同じ『同一コード・項目別文言』の方針）。
-失敗原因（署名不正・期限切れなど）は応答に出さない。
-SecurityConfig で http.exceptionHandling(...) と oauth2ResourceServer(...).authenticationEntryPoint(...) の両方に設定する（Bearer トークン不正と未認証の両方を拾うため）。</t>
+          <t>HttpServletResponse#getWriter</t>
         </is>
       </c>
       <c r="C53" s="9" t="n"/>
@@ -4498,44 +5189,46 @@
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="10" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>6.5  RestAccessDeniedHandler#handle</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="10" t="n"/>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Security（AccessDeniedHandler。共通基盤への追加改修）</t>
-        </is>
-      </c>
+    <row r="54" ht="109" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>専用クラス（RestAuthenticationEntryPoint 等）は作らず、SecurityConfig 内のラムダで実装する（実装済み）。
+コードは E-001（認証失敗）を使う。KF-BD-006 の E-001 は『メールアドレスまたはパスワードが正しくありません。』だが、トークンなし・不正・期限切れの文言としては不適切なため、E-001 の項目別文言として『認証が必要です。再度ログインしてください。』を使う（同一コード・項目別文言の方針）。
+失敗原因（署名不正・期限切れなど）は応答に出さない。
+oauth2ResourceServer(...) の entryPoint / accessDeniedHandler は、トークン不正（Bearer あり）と認証なし（Bearer なし）の両方に適用される。</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>6.5  DevDataInitializer#run</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n"/>
       <c r="C56" s="9" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="10" t="n"/>
     </row>
-    <row r="57" ht="34" customHeight="1">
+    <row r="57" ht="19" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>@Override
-public void handle(HttpServletRequest request, HttpServletResponse response, AccessDeniedException ex) throws IOException</t>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Initializer（CommandLineRunner。開発用）</t>
         </is>
       </c>
       <c r="C57" s="9" t="n"/>
@@ -4543,15 +5236,16 @@
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="10" t="n"/>
     </row>
-    <row r="58" ht="19" customHeight="1">
+    <row r="58" ht="34" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>認証済みだが権限が足りない場合（フィルタ段階の認可）の応答を、共通の ErrorResponse（403 / E-010）で返す。</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>@Override
+public void run(String... args)</t>
         </is>
       </c>
       <c r="C58" s="9" t="n"/>
@@ -4562,12 +5256,12 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>アノテーション</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>クラス: @Component（SecurityConfig から注入）</t>
+          <t>開発用ユーザー 100 名を投入する。kintaiflow.dev.seed-password が未設定、または users に 1 件でもあれば何もしない。</t>
         </is>
       </c>
       <c r="C59" s="9" t="n"/>
@@ -4576,39 +5270,35 @@
       <c r="F59" s="10" t="n"/>
     </row>
     <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>クラス: @Component, @Order(1)（BootstrapAdminInitializer より先に実行）</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="10" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>request</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>HttpServletRequest</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="D61" s="9" t="n"/>
@@ -4618,17 +5308,17 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>response</t>
+          <t>args</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>HttpServletResponse</t>
+          <t>String...</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>レスポンス</t>
+          <t>起動引数（未使用）</t>
         </is>
       </c>
       <c r="D62" s="9" t="n"/>
@@ -4636,21 +5326,17 @@
       <c r="F62" s="10" t="n"/>
     </row>
     <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>ex</t>
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>AccessDeniedException</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>権限不足の原因（応答には出さない）</t>
-        </is>
-      </c>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n"/>
       <c r="D63" s="9" t="n"/>
       <c r="E63" s="9" t="n"/>
       <c r="F63" s="10" t="n"/>
@@ -4658,7 +5344,7 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -4674,12 +5360,12 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>IOException</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>コード例は「6.x DevDataInitializer#run」を参照</t>
         </is>
       </c>
       <c r="C65" s="9" t="n"/>
@@ -4687,18 +5373,15 @@
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="10" t="n"/>
     </row>
-    <row r="66" ht="64" customHeight="1">
+    <row r="66" ht="19" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>response.setStatus(HttpServletResponse.SC_FORBIDDEN);                           // 403
-response.setContentType("application/json;charset=UTF-8");
-ErrorResponse body = new ErrorResponse("E-010", "この操作を行う権限がありません。", List.of());
-objectMapper.writeValue(response.getWriter(), body);</t>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>UserRepository#count / UserRepository#saveAll / PasswordEncoder#encode</t>
         </is>
       </c>
       <c r="C66" s="9" t="n"/>
@@ -4706,15 +5389,16 @@
       <c r="E66" s="9" t="n"/>
       <c r="F66" s="10" t="n"/>
     </row>
-    <row r="67" ht="19" customHeight="1">
+    <row r="67" ht="79" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>ObjectMapper#writeValue</t>
+          <t>全員同じ seed-password を BCrypt で 1 回だけハッシュ化して使い回す（100 回 encode しない）。上長（MANAGER）を先に saveAll して id を確定させ、その id を一般職の manager_id に設定してから saveAll する（manager_id が自己参照 FK のため）。メソッドに @Transactional は付けない（saveAll は Repository 側のトランザクション。2 回の saveAll は別トランザクション）。
+本番（DEV_SEED_PASSWORD 未設定）では何もしない。氏名は姓 20 種×名 20 種から機械的に生成し、入社日は 2016/04/01 からの日数ずらし（架空データ）。</t>
         </is>
       </c>
       <c r="C67" s="9" t="n"/>
@@ -4722,43 +5406,44 @@
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="10" t="n"/>
     </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>@PreAuthorize 由来の AccessDeniedException はコントローラ内で投げられるため、本ハンドラではなく GlobalExceptionHandler#handleAccessDenied が受ける（下表）。本ハンドラはフィルタ段階（requestMatchers の認可）の権限不足用で、どちらも同じ 403 / E-010 / 文言にそろえる。</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="9" t="n"/>
-      <c r="F68" s="10" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>6.6  EmailNormalizer#normalize</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="n"/>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>6.6  BootstrapAdminInitializer#run</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="10" t="n"/>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Initializer（CommandLineRunner。初期管理者作成）</t>
+        </is>
+      </c>
       <c r="C70" s="9" t="n"/>
       <c r="D70" s="9" t="n"/>
       <c r="E70" s="9" t="n"/>
       <c r="F70" s="10" t="n"/>
     </row>
-    <row r="71" ht="19" customHeight="1">
+    <row r="71" ht="34" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Utility（util）</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>@Override
+public void run(String... args)</t>
         </is>
       </c>
       <c r="C71" s="9" t="n"/>
@@ -4769,12 +5454,12 @@
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>public static String normalize(String email)</t>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>本番の初回起動で、users が空の場合に限り、設定値から初期管理者（ADMIN）を 1 名作成する。</t>
         </is>
       </c>
       <c r="C72" s="9" t="n"/>
@@ -4782,15 +5467,15 @@
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="10" t="n"/>
     </row>
-    <row r="73" ht="34" customHeight="1">
+    <row r="73" ht="19" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>メールアドレスを保存・検索用に正規化する（前後の空白を除去し、小文字にする）。ログイン検索（ONL-001）とユーザー登録・更新・一覧検索（ONL-014）で共通に使う。</t>
+          <t>クラス: @Component, @Order(2)（DevDataInitializer の後に実行）</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -4799,35 +5484,39 @@
       <c r="F73" s="10" t="n"/>
     </row>
     <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>クラス: final（static メソッドのみ）</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="n"/>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D74" s="9" t="n"/>
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="10" t="n"/>
     </row>
     <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>args</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>String...</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>起動引数（未使用）</t>
         </is>
       </c>
       <c r="D75" s="9" t="n"/>
@@ -4835,21 +5524,17 @@
       <c r="F75" s="10" t="n"/>
     </row>
     <row r="76" ht="19" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>入力されたメールアドレス（null 可）</t>
-        </is>
-      </c>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n"/>
       <c r="D76" s="9" t="n"/>
       <c r="E76" s="9" t="n"/>
       <c r="F76" s="10" t="n"/>
@@ -4857,12 +5542,12 @@
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>String（正規化後。null の場合は null）</t>
+          <t>IllegalStateException（パスワードがポリシー違反のとき。起動失敗＝fail-fast）</t>
         </is>
       </c>
       <c r="C77" s="9" t="n"/>
@@ -4870,15 +5555,27 @@
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="10" t="n"/>
     </row>
-    <row r="78" ht="19" customHeight="1">
+    <row r="78" ht="214" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>if (email.isBlank() || password.isBlank() || userRepository.count() &gt; 0) return;   // 設定が揃っていない or 既にユーザーあり → 何もしない
+String problem = AuthService.validatePolicy(password, "");              // 現在のパスワードは無いので "" を渡す
+if (problem != null)
+    throw new IllegalStateException("初期管理者のパスワードがポリシーを満たしません: " + problem);   // fail-fast
+User u = new User();
+u.setEmail(email.trim().toLowerCase(Locale.ROOT));
+u.setPasswordHash(passwordEncoder.encode(password));
+u.setName("システム管理者"); u.setRole("ADMIN"); u.setStatus("ACTIVE");
+u.setDepartmentId(1L);                      // 管理部（V1 の初期データ id=1）
+u.setHireDate(LocalDate.now());             // コンテナの TZ=Asia/Tokyo 前提
+u.setMustChangePassword(true);              // 初回ログイン後にパスワード変更を強制（画面側の誘導）
+userRepository.save(u);
+log.info("Bootstrap admin created: {}", u.getEmail());</t>
         </is>
       </c>
       <c r="C78" s="9" t="n"/>
@@ -4886,16 +5583,15 @@
       <c r="E78" s="9" t="n"/>
       <c r="F78" s="10" t="n"/>
     </row>
-    <row r="79" ht="34" customHeight="1">
+    <row r="79" ht="19" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>if (email == null) return null;
-return email.trim().toLowerCase(Locale.ROOT);   // Locale.ROOT：トルコ語ロケール等の影響を受けない</t>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>UserRepository#count / AuthService#validatePolicy / PasswordEncoder#encode / UserRepository#save</t>
         </is>
       </c>
       <c r="C79" s="9" t="n"/>
@@ -4903,15 +5599,18 @@
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="10" t="n"/>
     </row>
-    <row r="80" ht="19" customHeight="1">
+    <row r="80" ht="124" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>String#trim / String#toLowerCase(Locale.ROOT)</t>
+          <t>実行条件は『users が空』かつ『admin-email と admin-password の両方が設定済み』。開発環境では DevDataInitializer（@Order(1)）が先にユーザーを投入するため、users が空でなくなり本処理は何もしない。
+ポリシー違反の初期パスワードは起動を止めて気付けるようにする（弱いパスワードの管理者を作らない）。validatePolicy の第 2 引数（現在のパスワード）は空文字（""）を渡す（新パスワードと一致しないため比較は常に不一致）。
+作成後は ADMIN が初回ログインし、mustChangePassword=true によりパスワード変更（ONL-023）へ誘導される。初期パスワード（BOOTSTRAP_ADMIN_PASSWORD）は .env（Git 管理外）に置き、変更後は不要。
+実装メモ：メソッドに @Transactional は付けない（save は Repository 側のトランザクション）。ログには管理者のメールアドレスを出力する（パスワードは出さない）。</t>
         </is>
       </c>
       <c r="C80" s="9" t="n"/>
@@ -4919,31 +5618,29 @@
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="10" t="n"/>
     </row>
-    <row r="81" ht="64" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Locale.ROOT を必ず指定する（既定ロケールだと "I" が "ı" になる環境がある）。
-既存データに大文字を含むメールアドレスがある場合は、導入時に UPDATE users SET email = LOWER(TRIM(email)) を1回実行する（正規化後に重複する場合は事前に手動で解消する。uq_users_1 に違反するため）。
-形式（@ の有無など）の検証はしない。ログインでは存在しなければ E-001、ユーザー登録は ONL-014 の入力チェック（E-002）で行う。</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="10" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>6.7  UserRepository#findByEmail</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="n"/>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>6.7  EmailNormalizer#normalize</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Utility（util）【未実装・設計案】</t>
+        </is>
+      </c>
       <c r="C83" s="9" t="n"/>
       <c r="D83" s="9" t="n"/>
       <c r="E83" s="9" t="n"/>
@@ -4952,12 +5649,12 @@
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Repository（Spring Data JPA）</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>public static String normalize(String email)</t>
         </is>
       </c>
       <c r="C84" s="9" t="n"/>
@@ -4965,15 +5662,15 @@
       <c r="E84" s="9" t="n"/>
       <c r="F84" s="10" t="n"/>
     </row>
-    <row r="85" ht="19" customHeight="1">
+    <row r="85" ht="34" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Optional&lt;User&gt; findByEmail(String email)</t>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>メールアドレスを保存・検索用に正規化する（前後の空白を除去し、小文字にする）。現行コードにはこのクラスは無く、ログイン（AuthService#login）が同じ処理を直接行っている。ユーザー登録・更新・一覧検索（ONL-014）の実装時に、ログインと共通化するために作成する。</t>
         </is>
       </c>
       <c r="C85" s="9" t="n"/>
@@ -4984,12 +5681,12 @@
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>正規化済み（trim＋小文字）のメールアドレスが完全一致するユーザーを1件返す。</t>
+          <t>クラス: final（static メソッドのみ）</t>
         </is>
       </c>
       <c r="C86" s="9" t="n"/>
@@ -4998,35 +5695,39 @@
       <c r="F86" s="10" t="n"/>
     </row>
     <row r="87" ht="19" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>interface UserRepository extends JpaRepository&lt;User, Long&gt;</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="n"/>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="10" t="n"/>
     </row>
     <row r="88" ht="19" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>入力されたメールアドレス（null 可）</t>
         </is>
       </c>
       <c r="D88" s="9" t="n"/>
@@ -5034,21 +5735,17 @@
       <c r="F88" s="10" t="n"/>
     </row>
     <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>検索するメールアドレス（呼出し側で EmailNormalizer#normalize 済みのもの）</t>
-        </is>
-      </c>
+          <t>String（正規化後。null の場合は null）</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n"/>
       <c r="D89" s="9" t="n"/>
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="10" t="n"/>
@@ -5056,12 +5753,12 @@
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Optional&lt;User&gt;（該当なしは Optional.empty()）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C90" s="9" t="n"/>
@@ -5069,15 +5766,16 @@
       <c r="E90" s="9" t="n"/>
       <c r="F90" s="10" t="n"/>
     </row>
-    <row r="91" ht="19" customHeight="1">
+    <row r="91" ht="34" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>if (email == null) return null;
+return email.trim().toLowerCase(Locale.ROOT);   // Locale.ROOT：トルコ語ロケール等の影響を受けない</t>
         </is>
       </c>
       <c r="C91" s="9" t="n"/>
@@ -5085,16 +5783,15 @@
       <c r="E91" s="9" t="n"/>
       <c r="F91" s="10" t="n"/>
     </row>
-    <row r="92" ht="34" customHeight="1">
+    <row r="92" ht="19" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>実装クラスは作らない。メソッド名から Spring Data JPA が次の SQL を生成する。
-SELECT * FROM users WHERE email = ?</t>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>String#trim / String#toLowerCase(Locale.ROOT)</t>
         </is>
       </c>
       <c r="C92" s="9" t="n"/>
@@ -5102,15 +5799,18 @@
       <c r="E92" s="9" t="n"/>
       <c r="F92" s="10" t="n"/>
     </row>
-    <row r="93" ht="19" customHeight="1">
+    <row r="93" ht="94" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>（DB: users）</t>
+          <t>【実装状況】未実装。ONL-001 の実コードは request.email().trim().toLowerCase(Locale.ROOT) をインライン実行している（動作は本メソッドと同一）。ONL-014 実装時に AuthService もこのメソッドへ置き換える。
+Locale.ROOT を必ず指定する（既定ロケールだと "I" が "ı" になる環境がある）。
+既存データに大文字を含むメールアドレスがある場合は、導入時に UPDATE users SET email = LOWER(TRIM(email)) を1回実行する（正規化後に重複する場合は事前に手動で解消する。uq_users_1 に違反するため）。
+形式（@ の有無など）の検証はしない。ログインでは存在しなければ E-001、ユーザー登録は ONL-014 の入力チェック（E-002）で行う。</t>
         </is>
       </c>
       <c r="C93" s="9" t="n"/>
@@ -5118,29 +5818,29 @@
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="10" t="n"/>
     </row>
-    <row r="94" ht="34" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>users.email は UNIQUE 制約（uq_users_1）のため結果は最大1件。DB への比較は完全一致だが、保存時・検索時とも EmailNormalizer#normalize（trim＋toLowerCase(Locale.ROOT)）で正規化した値を使うため、実質的に大文字小文字を区別しない（メールアドレスは常に小文字で保存される）。</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="9" t="n"/>
-      <c r="E94" s="9" t="n"/>
-      <c r="F94" s="10" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>6.8  JwtService#issue</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="n"/>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>6.8  UserRepository#findByEmail</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Repository（Spring Data JPA）</t>
+        </is>
+      </c>
       <c r="C96" s="9" t="n"/>
       <c r="D96" s="9" t="n"/>
       <c r="E96" s="9" t="n"/>
@@ -5149,12 +5849,12 @@
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Service（security）</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Optional&lt;User&gt; findByEmail(String email)</t>
         </is>
       </c>
       <c r="C97" s="9" t="n"/>
@@ -5165,12 +5865,12 @@
     <row r="98" ht="19" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>public String issue(User user)</t>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>正規化済み（trim＋小文字）のメールアドレスが完全一致するユーザーを1件返す。</t>
         </is>
       </c>
       <c r="C98" s="9" t="n"/>
@@ -5181,12 +5881,12 @@
     <row r="99" ht="19" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>ユーザー情報から署名付き JWT を生成して文字列で返す。</t>
+          <t>interface UserRepository extends JpaRepository&lt;User, Long&gt;</t>
         </is>
       </c>
       <c r="C99" s="9" t="n"/>
@@ -5195,35 +5895,39 @@
       <c r="F99" s="10" t="n"/>
     </row>
     <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>クラス: @Service</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="n"/>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D100" s="9" t="n"/>
       <c r="E100" s="9" t="n"/>
       <c r="F100" s="10" t="n"/>
     </row>
     <row r="101" ht="19" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>検索するメールアドレス（呼出し側で trim＋小文字化済みのもの）</t>
         </is>
       </c>
       <c r="D101" s="9" t="n"/>
@@ -5231,21 +5935,17 @@
       <c r="F101" s="10" t="n"/>
     </row>
     <row r="102" ht="19" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>user</t>
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>認証済みユーザー（id / role を使用）</t>
-        </is>
-      </c>
+          <t>Optional&lt;User&gt;（該当なしは Optional.empty()）</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n"/>
       <c r="D102" s="9" t="n"/>
       <c r="E102" s="9" t="n"/>
       <c r="F102" s="10" t="n"/>
@@ -5253,12 +5953,12 @@
     <row r="103" ht="19" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>String（JWT。ヘッダ.ペイロード.署名）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C103" s="9" t="n"/>
@@ -5266,15 +5966,16 @@
       <c r="E103" s="9" t="n"/>
       <c r="F103" s="10" t="n"/>
     </row>
-    <row r="104" ht="19" customHeight="1">
+    <row r="104" ht="34" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>実装クラスは作らない。メソッド名から Spring Data JPA が次の SQL を生成する。
+SELECT * FROM users WHERE email = ?</t>
         </is>
       </c>
       <c r="C104" s="9" t="n"/>
@@ -5282,13 +5983,193 @@
       <c r="E104" s="9" t="n"/>
       <c r="F104" s="10" t="n"/>
     </row>
-    <row r="105" ht="154" customHeight="1">
+    <row r="105" ht="19" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>（DB: users）</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="10" t="n"/>
+    </row>
+    <row r="106" ht="49" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>users.email は UNIQUE 制約（uq_users_1）のため結果は最大1件。DB への比較は完全一致だが、保存時・検索時とも trim＋toLowerCase(Locale.ROOT) で正規化した値を使う（ログインは AuthService#login 内で直接実行、登録は ONL-014）ため、実質的に大文字小文字を区別しない（メールアドレスは常に小文字で保存される）。</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>6.9  JwtService#issue</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="10" t="n"/>
+    </row>
+    <row r="109" ht="19" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Service（security）</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="10" t="n"/>
+    </row>
+    <row r="110" ht="19" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>public String issue(User user)</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="10" t="n"/>
+    </row>
+    <row r="111" ht="19" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー情報から署名付き JWT を生成して文字列で返す。</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="n"/>
+      <c r="D111" s="9" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="10" t="n"/>
+    </row>
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>クラス: @Service</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="10" t="n"/>
+    </row>
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="10" t="n"/>
+    </row>
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>認証済みユーザー（id / role を使用）</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="10" t="n"/>
+    </row>
+    <row r="115" ht="19" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>String（JWT。ヘッダ.ペイロード.署名）</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="9" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="10" t="n"/>
+    </row>
+    <row r="116" ht="19" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="10" t="n"/>
+    </row>
+    <row r="117" ht="154" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
           <t>処理詳細</t>
         </is>
       </c>
-      <c r="B105" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t>now = Instant.now()
 claims = JwtClaimsSet.builder()
@@ -5302,496 +6183,284 @@
 return encoder.encode(JwtEncoderParameters.from(header, claims)).getTokenValue()</t>
         </is>
       </c>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-      <c r="F105" s="10" t="n"/>
-    </row>
-    <row r="106" ht="19" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="10" t="n"/>
+    </row>
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>呼出先</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>JwtEncoder#encode（SecurityConfig の Bean）</t>
         </is>
       </c>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="9" t="n"/>
-      <c r="E106" s="9" t="n"/>
-      <c r="F106" s="10" t="n"/>
-    </row>
-    <row r="107" ht="34" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>expirationHours は @Value("${kintaiflow.jwt.expiration-hours}") でコンストラクタ注入（既定 8）。
-トークンにパスワードやメールアドレスを入れない。</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="n"/>
-      <c r="D107" s="9" t="n"/>
-      <c r="E107" s="9" t="n"/>
-      <c r="F107" s="10" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>6.9  GlobalExceptionHandler（例外 → 共通エラー応答）</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="9" t="n"/>
-      <c r="D109" s="9" t="n"/>
-      <c r="E109" s="9" t="n"/>
-      <c r="F109" s="10" t="n"/>
-    </row>
-    <row r="110" ht="19" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>ハンドラ</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>対象例外</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>handleBusiness</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>BusinessException</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>例外が持つ status</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>例外が持つ code</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>例外が持つ message</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>E-001 はここで 401 になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="49" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>handleValidation</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>MethodArgumentNotValidException</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
-        <is>
-          <t>E-002</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>最初の項目エラーのメッセージ（無ければ「入力内容が正しくありません。」）</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>fieldErrors に全項目分を設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="34" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>handleUnreadable</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>HttpMessageNotReadableException</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>E-002</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>入力内容が正しくありません。</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>JSON 不正・本文なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="49" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>handleOther</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>E-012</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>log.error でスタックトレースを記録。画面には詳細を出さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="94" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>handleAccessDenied</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>AccessDeniedException</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>E-010</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>この操作を行う権限がありません。</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>@PreAuthorize（@EnableMethodSecurity）の権限不足。これが無いと handleOther が拾って 500 / E-012 になる。ONL-009/014 以降の全 ADMIN・MANAGER 専用 API が前提とする</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="79" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>handleTypeMismatch</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>MethodArgumentTypeMismatchException / MissingServletRequestParameterException</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>E-002</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>入力内容が正しくありません。</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>パス・クエリパラメータの型不一致・必須パラメータ欠落（例 /api/notifications/abc/read）。これが無いと handleOther が拾って 500 / E-012 になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>6.10  SecurityConfig（Bean 定義）</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="n"/>
       <c r="C118" s="9" t="n"/>
       <c r="D118" s="9" t="n"/>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="10" t="n"/>
     </row>
-    <row r="119" ht="19" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Bean</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+    <row r="119" ht="34" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>expirationHours は @Value("${kintaiflow.jwt.expiration-hours}") でコンストラクタ注入（application.properties の値は 2）。
+トークンにパスワードやメールアドレスを入れない。</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="n"/>
       <c r="D119" s="9" t="n"/>
       <c r="E119" s="9" t="n"/>
       <c r="F119" s="10" t="n"/>
     </row>
-    <row r="120" ht="19" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>passwordEncoder</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>PasswordEncoder</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>new BCryptPasswordEncoder()（強度は既定値）</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="n"/>
-      <c r="E120" s="9" t="n"/>
-      <c r="F120" s="10" t="n"/>
-    </row>
-    <row r="121" ht="19" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>jwtSecretKey</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>SecretKey</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>kintaiflow.jwt.secret（Base64）をデコードし HmacSHA256 の鍵にする</t>
-        </is>
-      </c>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>6.10  GlobalExceptionHandler（例外 → 共通エラー応答）</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="9" t="n"/>
       <c r="D121" s="9" t="n"/>
       <c r="E121" s="9" t="n"/>
       <c r="F121" s="10" t="n"/>
     </row>
     <row r="122" ht="19" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>jwtEncoder</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>JwtEncoder</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>NimbusJwtEncoder(new ImmutableSecret&lt;&gt;(jwtSecretKey))</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="n"/>
-      <c r="E122" s="9" t="n"/>
-      <c r="F122" s="10" t="n"/>
-    </row>
-    <row r="123" ht="19" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>ハンドラ</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>対象例外</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="34" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>jwtDecoder</t>
+          <t>handleBusiness</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>JwtDecoder</t>
+          <t>BusinessException</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>NimbusJwtDecoder.withSecretKey(key).macAlgorithm(HS256).build()</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="n"/>
-      <c r="E123" s="9" t="n"/>
-      <c r="F123" s="10" t="n"/>
-    </row>
-    <row r="124" ht="34" customHeight="1">
+          <t>例外が持つ status</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>例外が持つ code</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>例外が持つ message</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>E-001（401）・E-017（423）・E-018（400）などはここで変換される</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="49" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>jwtAuthenticationConverter</t>
+          <t>handleValidation</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>JwtAuthenticationConverter</t>
+          <t>MethodArgumentNotValidException</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>claim "role" を権限 ROLE_&lt;role&gt; に変換（例: ROLE_ADMIN）</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="n"/>
-      <c r="E124" s="9" t="n"/>
-      <c r="F124" s="10" t="n"/>
-    </row>
-    <row r="125" ht="64" customHeight="1">
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>最初の項目エラーのメッセージ（無ければ「入力内容が正しくありません。」）</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>fieldErrors に全項目分を設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="34" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>securityFilterChain</t>
+          <t>handleUnreadable</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>SecurityFilterChain</t>
+          <t>HttpMessageNotReadableException</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>CSRF 無効 / CORS 有効 / セッション STATELESS / POST /api/auth/login は permitAll / それ以外は authenticated / JWT リソースサーバ。exceptionHandling に authenticationEntryPoint=RestAuthenticationEntryPoint・accessDeniedHandler=RestAccessDeniedHandler を設定し、oauth2ResourceServer(...).authenticationEntryPoint(同) も設定する</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="n"/>
-      <c r="E125" s="9" t="n"/>
-      <c r="F125" s="10" t="n"/>
-    </row>
-    <row r="126" ht="34" customHeight="1">
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>入力内容が正しくありません。</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>JSON 不正・本文なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="49" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>corsConfigurationSource</t>
+          <t>handleOther</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>CorsConfigurationSource</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>許可オリジン http://localhost:5173、メソッド GET,POST,PUT,DELETE,OPTIONS、ヘッダ Authorization,Content-Type（/api/** に適用）</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n"/>
-      <c r="F126" s="10" t="n"/>
-    </row>
-    <row r="127" ht="34" customHeight="1">
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>E-012</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>log.error でスタックトレースを記録。画面には詳細を出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="109" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>（クラス）@EnableMethodSecurity</t>
+          <t>handleAccessDenied</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>アノテーション</t>
+          <t>AccessDeniedException</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>SecurityConfig クラスに付与し @PreAuthorize を有効化する（後続 ONL の前提）</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="n"/>
-      <c r="E127" s="9" t="n"/>
-      <c r="F127" s="10" t="n"/>
-    </row>
-    <row r="128" ht="49" customHeight="1">
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>E-010</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>この操作を行う権限がありません。</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>@PreAuthorize（@EnableMethodSecurity）の権限不足。これが無いと handleOther が拾って 500 / E-012 になる。ONL-009/014 以降の全 ADMIN・MANAGER 専用 API が前提とする（現行コードでは未実装。該当 API の実装時に追加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="94" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>restAuthenticationEntryPoint / restAccessDeniedHandler</t>
+          <t>handleTypeMismatch</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>AuthenticationEntryPoint / AccessDeniedHandler</t>
+          <t>MethodArgumentTypeMismatchException / MissingServletRequestParameterException</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>@Component を SecurityConfig にコンストラクタ注入して securityFilterChain で使用</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="n"/>
-      <c r="E128" s="9" t="n"/>
-      <c r="F128" s="10" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>入力内容が正しくありません。</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>パス・クエリパラメータの型不一致・必須パラメータ欠落（例 /api/notifications/abc/read）。これが無いと handleOther が拾って 500 / E-012 になる（現行コードでは未実装。該当 API の実装時に追加）</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>6.11  共通基盤への追加改修（後続 ONL が前提とする。KF-DD-001「共通基盤への追加改修」と同内容）</t>
+          <t>6.11  SecurityConfig（Bean 定義）</t>
         </is>
       </c>
       <c r="B130" s="9" t="n"/>
@@ -5803,238 +6472,489 @@
     <row r="131" ht="19" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>対象</t>
+          <t>Bean</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>改修内容</t>
+          <t>型</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>必要とする処理</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132" ht="94" customHeight="1">
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="10" t="n"/>
+    </row>
+    <row r="132" ht="19" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>SecurityConfig</t>
+          <t>passwordEncoder</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>@EnableMethodSecurity を付与し、exceptionHandling / oauth2ResourceServer に RestAuthenticationEntryPoint・RestAccessDeniedHandler を設定する</t>
+          <t>PasswordEncoder</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>ONL-009〜012・014・015・016・017・018・020 ほか（@PreAuthorize 使用の全処理）</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>実装は ONL-001（本書）。後続 ONL で重複追加しない</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
-      <c r="F132" s="7" t="inlineStr"/>
-    </row>
-    <row r="133" ht="49" customHeight="1">
+          <t>new BCryptPasswordEncoder()（強度は既定値）</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="10" t="n"/>
+    </row>
+    <row r="133" ht="19" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint（新規）</t>
+          <t>jwtSecretKey</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>トークンなし・不正・期限切れを 401 / E-001 の JSON（ErrorResponse）で返す</t>
+          <t>SecretKey</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>全認証必須 API</t>
-        </is>
-      </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>KF-BD-006 の E-001 を項目別文言で使用</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr"/>
-      <c r="F133" s="7" t="inlineStr"/>
-    </row>
-    <row r="134" ht="49" customHeight="1">
+          <t>kintaiflow.jwt.secret（Base64）をデコードし HmacSHA256 の鍵にする</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n"/>
+      <c r="E133" s="9" t="n"/>
+      <c r="F133" s="10" t="n"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler（新規）</t>
+          <t>jwtEncoder</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す</t>
+          <t>JwtEncoder</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>全認証必須 API</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr"/>
-      <c r="E134" s="7" t="inlineStr"/>
-      <c r="F134" s="7" t="inlineStr"/>
-    </row>
-    <row r="135" ht="49" customHeight="1">
+          <t>NimbusJwtEncoder(new ImmutableSecret&lt;&gt;(jwtSecretKey))</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="10" t="n"/>
+    </row>
+    <row r="135" ht="19" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler#handleAccessDenied</t>
+          <t>jwtDecoder</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>AccessDeniedException → 403 / E-010</t>
+          <t>JwtDecoder</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>@PreAuthorize を使う全処理</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>handleOther より先に評価される具体的な例外型</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr"/>
-      <c r="F135" s="7" t="inlineStr"/>
-    </row>
-    <row r="136" ht="49" customHeight="1">
+          <t>NimbusJwtDecoder.withSecretKey(key).macAlgorithm(HS256).build()</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="10" t="n"/>
+    </row>
+    <row r="136" ht="34" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler#handleTypeMismatch</t>
+          <t>jwtAuthenticationConverter</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>MethodArgumentTypeMismatchException → 400 / E-002</t>
+          <t>JwtAuthenticationConverter</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>パスパラメータ・クエリパラメータを持つ全処理</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr"/>
-      <c r="E136" s="7" t="inlineStr"/>
-      <c r="F136" s="7" t="inlineStr"/>
+          <t>claim "role" を権限 ROLE_&lt;role&gt; に変換（例: ROLE_ADMIN）</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="10" t="n"/>
     </row>
     <row r="137" ht="49" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>EmailNormalizer（新規）</t>
+          <t>securityFilterChain</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>trim().toLowerCase(Locale.ROOT)。保存時・検索時に使用</t>
+          <t>SecurityFilterChain</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>ONL-001・ONL-014</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr"/>
-      <c r="E137" s="7" t="inlineStr"/>
-      <c r="F137" s="7" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>6.12  DevDataInitializer#run（開発用・本番では使用しない）</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="n"/>
-      <c r="C139" s="9" t="n"/>
+          <t>CSRF 無効 / CORS 有効 / セッション STATELESS / permitAll: POST /api/auth/login・GET /actuator/health（監視用。認証不要）/ それ以外は authenticated / JWT リソースサーバ。oauth2ResourceServer(...) に authenticationEntryPoint（401 / E-001）・accessDeniedHandler（403 / E-010）をラムダで設定し、writeError で JSON を返す</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="10" t="n"/>
+    </row>
+    <row r="138" ht="34" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>corsConfigurationSource</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>CorsConfigurationSource</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>許可オリジンは設定 kintaiflow.cors.allowed-origins（既定 http://localhost:5173、カンマ区切りで複数可）、メソッド GET,POST,PUT,DELETE,OPTIONS、ヘッダ Authorization,Content-Type（/api/** に適用）</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="10" t="n"/>
+    </row>
+    <row r="139" ht="34" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>（クラス）@EnableMethodSecurity</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>SecurityConfig クラスに付与し @PreAuthorize を有効化する（後続 ONL の前提。現行コードでは未付与で、@PreAuthorize を使う API の実装時に追加）</t>
+        </is>
+      </c>
       <c r="D139" s="9" t="n"/>
       <c r="E139" s="9" t="n"/>
       <c r="F139" s="10" t="n"/>
     </row>
-    <row r="140" ht="109" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t>if (seedPassword.isBlank() || userRepository.count() &gt; 0) return;   // 設定なし or 既にユーザーあり → 何もしない
-以下4ユーザーを作成（パスワードは全員 seedPassword を BCrypt でハッシュ化、status=ACTIVE、hire_date=2024-04-01）
-  admin@example.com   人事 管理者  ADMIN     department_id=1  manager_id=なし
-  manager@example.com 佐藤 一郎    MANAGER   department_id=2  manager_id=なし
-  taro@example.com    山田 太郎    EMPLOYEE  department_id=2  manager_id=佐藤の id
-  hanako@example.com  鈴木 花子    EMPLOYEE  department_id=2  manager_id=佐藤の id
-log.info("Dev seed users created (4 users).")</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="n"/>
+    <row r="140" ht="34" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>writeError（private static）</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>メソッド</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>401 / 403 の JSON（ErrorResponse 形式）を書き込む。securityFilterChain のラムダから使用</t>
+        </is>
+      </c>
       <c r="D140" s="9" t="n"/>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="10" t="n"/>
     </row>
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>6.12  共通基盤への追加改修（後続 ONL が前提とする。KF-DD-001「共通基盤への追加改修」と同内容）</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="10" t="n"/>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>改修内容</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>必要とする処理</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr"/>
+      <c r="F143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144" ht="154" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>SecurityConfig</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>@EnableMethodSecurity を付与し、oauth2ResourceServer に authenticationEntryPoint（401 / E-001）・accessDeniedHandler（403 / E-010）をラムダで設定する（401 / 403 は実装済み。@EnableMethodSecurity は @PreAuthorize を使う API の実装時）</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>ONL-009〜012・014・015・016・017・018・020 ほか（@PreAuthorize 使用の全処理）</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>実装は ONL-001（本書）。後続 ONL で重複追加しない</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145" ht="94" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>SecurityConfig#authenticationEntryPoint（実装済み）</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>トークンなし・不正・期限切れを 401 / E-001 の JSON（ErrorResponse）で返す。文言『認証が必要です。再度ログインしてください。』</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>全認証必須 API</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>KF-BD-006 の E-001 を項目別文言で使用</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146" ht="49" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>SecurityConfig#accessDeniedHandler（実装済み）</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>全認証必須 API</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr"/>
+      <c r="E146" s="7" t="inlineStr"/>
+      <c r="F146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147" ht="49" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler#handleAccessDenied</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>AccessDeniedException → 403 / E-010</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>@PreAuthorize を使う全処理</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>handleOther より先に評価される具体的な例外型</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr"/>
+      <c r="F147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148" ht="49" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler#handleTypeMismatch</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>MethodArgumentTypeMismatchException → 400 / E-002</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>パスパラメータ・クエリパラメータを持つ全処理</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr"/>
+      <c r="F148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149" ht="94" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>EmailNormalizer（新規・未実装。ONL-014 実装時に共通化）</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>trim().toLowerCase(Locale.ROOT)。保存時・検索時に使用。現行コードでは AuthService#login 内で直接実行（クラス化は ONL-014 実装時）</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>ONL-001・ONL-014</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr"/>
+      <c r="F149" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>6.13  DevDataInitializer#run（開発用・本番では使用しない。@Order(1)）</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="9" t="n"/>
+      <c r="D151" s="9" t="n"/>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="10" t="n"/>
+    </row>
+    <row r="152" ht="184" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>if (seedPassword.isBlank() || userRepository.count() &gt; 0) return;   // 設定なし or 既にユーザーあり → 何もしない
+全員のパスワードは seedPassword を BCrypt でハッシュ化した同一ハッシュ、status=ACTIVE、must_change_password=false（既定）。
+計 100 名（上長を先に saveAll して id を確定 → 一般職の manager_id に設定して saveAll）：
+  管理部（department_id=1）10 名：ADMIN 2（admin@example.com「人事 管理者」/ adm002@example.com）、MANAGER 1（adm003@example.com）、EMPLOYEE 7（adm004〜adm010@example.com。上長は adm003）
+  システム開発事業部（2）30 名：MANAGER 2（manager@example.com「佐藤 一郎」/ dev002@example.com）＋ EMPLOYEE 28（taro@example.com「山田 太郎」・hanako@example.com「鈴木 花子」＝上長は manager@、dev005〜dev030@example.com）
+  ソリューション事業部（3）25 名：MANAGER 2（sol001・sol002）＋ EMPLOYEE 23（sol003〜sol025@example.com）
+  SAP事業部（4）20 名：MANAGER 2（sap001・sap002）＋ EMPLOYEE 18（sap003〜sap020@example.com）
+  クラウド基盤サービス部（5）15 名：MANAGER 2（cld001・cld002）＋ EMPLOYEE 13（cld003〜cld015@example.com）
+  技術部門の一般職の上長は、番号が偶数なら 1 人目の MANAGER、奇数なら 2 人目の MANAGER。
+log.info("Dev seed users created ({} users).", 100);</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>6.14  BootstrapAdminInitializer#run（本番の初期管理者。@Order(2)）</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="9" t="n"/>
+      <c r="F154" s="10" t="n"/>
+    </row>
+    <row r="155" ht="94" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>if (email.isBlank() || password.isBlank() || userRepository.count() &gt; 0) return;
+problem = AuthService.validatePolicy(password, "");
+if (problem != null) throw new IllegalStateException(...);   // 起動失敗（fail-fast）
+ADMIN を 1 名作成： name=「システム管理者」、email=小文字化、department_id=1、hire_date=今日（LocalDate.now()）、status=ACTIVE、must_change_password=true
+log.info("Bootstrap admin created: {}", email);   // メールアドレスのみ出力。パスワードは出さない</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="127">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="C61:F61"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="C122:F122"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A118:F118"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="C125:F125"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="C136:F136"/>
+    <mergeCell ref="C87:F87"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C89:F89"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A121:F121"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C88:F88"/>
+    <mergeCell ref="B116:F116"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="B26:F26"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="C134:F134"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B118:F118"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A70:F70"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="C135:F135"/>
     <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="A28:F28"/>
@@ -6042,67 +6962,76 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="C124:F124"/>
+    <mergeCell ref="C137:F137"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C139:F139"/>
+    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="C123:F123"/>
-    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C138:F138"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C119:F119"/>
+    <mergeCell ref="C132:F132"/>
+    <mergeCell ref="B109:F109"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="A109:F109"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="C45:F45"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="C128:F128"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="C100:F100"/>
     <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C133:F133"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C114:F114"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="B110:F110"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B100:F100"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B140:F140"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="C131:F131"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="C140:F140"/>
     <mergeCell ref="B86:F86"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="B117:F117"/>
     <mergeCell ref="C101:F101"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="C74:F74"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="C126:F126"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B112:F112"/>
     <mergeCell ref="A130:F130"/>
-    <mergeCell ref="B49:F49"/>
     <mergeCell ref="C75:F75"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B89:F89"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B35:F35"/>
@@ -6118,7 +7047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F26"/>
+  <dimension ref="A2:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6217,7 +7146,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>email</t>
@@ -6240,7 +7169,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>○ 検索条件</t>
+          <t>○ 検索条件（正規化済み）</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -6469,269 +7398,606 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="49" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>failed_login_count</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>failedLoginCount</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>○ 判定・更新（不一致で +1、5 回目は 0 に戻す、成功時に 0）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>INT NOT NULL DEFAULT 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="79" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>locked_until</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>lockedUntil</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>○ ロック判定（&gt; 現在日時(JST) でロック中）・更新（5 回目の失敗で +30 分、成功時に NULL）</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="49" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力（LoginResponse）</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>BOOLEAN NOT NULL DEFAULT FALSE。ONL-023 で false に更新、ONL-014（登録）・BootstrapAdminInitializer で true</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>password_changed_at</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>passwordChangedAt</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP NULL。ONL-023 で更新（本処理では使わない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="49" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="49" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>ユーザー検索（UserRepository#findByEmail）</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE email = ?</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="49" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>パスワード不一致時の失敗回数更新（UserRepository#save）</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE users SET failed_login_count=?, locked_until=? WHERE id=?   -- 5 回目は locked_until=現在+30分, failed_login_count=0
+※ Hibernate は全更新対象列を更新する。updated_at はトリガで自動更新</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>ログイン成功時の失敗回数リセット（UserRepository#save。値が変わる場合のみ）</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE users SET failed_login_count=0, locked_until=NULL WHERE id=?</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="79" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>spring.datasource.url</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>jdbc:postgresql://localhost:5432/kintaiflow</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>jdbc:postgresql://localhost:5432/kintaiflow（compose では環境変数 SPRING_DATASOURCE_URL で db コンテナへ）</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="7" t="inlineStr"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="49" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>spring.datasource.password</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>application-local.properties</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>application-local.properties／環境変数 SPRING_DATASOURCE_PASSWORD</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>DB パスワード</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Git 管理外。値を文書・チャットに書かない</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="94" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>spring.flyway.enabled / baseline-on-migrate / baseline-version</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>true / true / 1。DB は Flyway（db/migration/V1__init_schema.sql）が作成する。旧 schema.sql で作成済みの DB は V1 適用済みとして取り込む</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>V1 は書き換えない。変更は V2__*.sql を追加（KF-DD-006）。旧 DB に users の新 4 列が無い場合は validate で起動失敗するため reset-dev.sql で作り直す</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>spring.jpa.hibernate.ddl-auto</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>validate（Entity と DB の整合を起動時に検証するだけ。DDL は自動生成しない）</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="7" t="inlineStr"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="79" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>SET TIME ZONE 'Asia/Tokyo'（DB セッションの時刻を JST に固定。locked_until 等の壁時計時刻と整合させる）</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="79" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>kintaiflow.jwt.secret</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>application-local.properties</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>application-local.properties／環境変数 KINTAIFLOW_JWT_SECRET（compose では .env の JWT_SECRET）</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>JWT 署名鍵（Base64、32バイト以上）</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Git 管理外</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>kintaiflow.jwt.expiration-hours</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>トークン有効時間（時間）。8</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>変更時は本書と KF-DD-001 を改訂</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>トークン有効時間（時間）。2</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>変更時は本書・KF-DD-006・KF-BD-010 を改訂</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="79" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>kintaiflow.dev.seed-password</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>application-local.properties</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>開発用ユーザーの初期パスワード</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>未設定ならユーザー投入しない。Git 管理外</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>application-local.properties／環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（compose では .env の DEV_SEED_PASSWORD）</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>開発用ユーザー 100 名の初期パスワード</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>未設定（本番）ならユーザー投入しない。Git 管理外</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="49" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>kintaiflow.cors.allowed-origins</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>許可オリジン（カンマ区切り）。既定 http://localhost:5173</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>本番は画面の URL に合わせる（Docker 構成は同一オリジン経由のため通常不要）</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>kintaiflow.bootstrap.admin-email</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_EMAIL（compose では .env の BOOTSTRAP_ADMIN_EMAIL）</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>初期管理者のメールアドレス</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>未設定なら初期管理者を作らない。Git 管理外（.env）</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="79" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>kintaiflow.bootstrap.admin-password</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_PASSWORD（compose では .env の BOOTSTRAP_ADMIN_PASSWORD）</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>初期管理者の初期パスワード（12 文字以上・英字と数字を含む）</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ポリシー違反なら起動失敗。Git 管理外（.env）。初回ログイン後に変更させる</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>management.endpoints.web.exposure.include</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>health（/actuator/health を公開。認証不要。management.endpoint.health.probes.enabled=true）</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Docker のヘルスチェック・監視用</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-001_ログイン_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-001_ログイン_オンライン詳細設計書.xlsx
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E27"/>
+  <dimension ref="A2:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1277,8 +1277,38 @@
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="10" t="n"/>
     </row>
+    <row r="28" ht="49" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>初期パスワードの強制（E-019）</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>ログイン応答の mustChangePassword=true のユーザーのトークンには mcp=true を入れる。PasswordChangeRequiredFilter は mcp=true のトークンで /api/auth/password 以外を呼ぶと 403 / E-019「初期パスワードのままです。先にパスワードを変更してください。」を返す（画面だけでなくサーバー側でも強制）。</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>発行済みトークンの失効</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>ActiveUserFilter：JWT の sub のユーザーが存在し ACTIVE であること、かつトークンの発行時刻がパスワード変更時刻（秒切捨て）以降であることを毎リクエスト確認する。無効化・削除・パスワード変更/再設定後の古いトークンは 401 / E-001。</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B26:E26"/>
@@ -1286,10 +1316,12 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B29:E29"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="B22:E22"/>
   </mergeCells>
